--- a/Plan/PERT Sheet .xlsx
+++ b/Plan/PERT Sheet .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stuartbaker/Desktop/University/Year2/Software Engineering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C2E3D2C-F37D-5646-AABB-864485E6D9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93F180D2-BFA7-8C40-9E82-DC8D50C842ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15980" xr2:uid="{409E12EB-2986-7040-875A-ECA154068229}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="95">
   <si>
     <t>Task</t>
   </si>
@@ -288,6 +288,39 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>Ontime Completion?</t>
+  </si>
+  <si>
+    <t>Yes, day 3</t>
+  </si>
+  <si>
+    <t>Yes, day 6</t>
+  </si>
+  <si>
+    <t>Yes, day 9</t>
+  </si>
+  <si>
+    <t>Yes, day 12</t>
+  </si>
+  <si>
+    <t>Misinterpretation and ambiguity in the specification led to questions being raised to Mr Raffles for clarity</t>
+  </si>
+  <si>
+    <t>Setbacks and Reasons</t>
+  </si>
+  <si>
+    <t>Yes, day 15</t>
+  </si>
+  <si>
+    <t>Took longer than planned due to illness and misreading the brief. At first we thought we designed our own board, but then we realised there was an excel sheet stating the different tile properties</t>
+  </si>
+  <si>
+    <t>Yes, day 16</t>
+  </si>
+  <si>
+    <t>Later start for this as we were focussed on other aspects of the game. This was not a priority at the time and also wasn't part of the critical path so we had some slack time.</t>
   </si>
 </sst>
 </file>
@@ -368,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -377,19 +410,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -724,21 +755,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904A3F7C-A719-FE4F-BE6A-42977A5F0A83}">
-  <dimension ref="B2:J23"/>
+  <dimension ref="B2:L23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="82.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="20" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" ht="20" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -766,15 +799,21 @@
       <c r="J2" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="3" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="3">
         <v>3</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -792,18 +831,22 @@
       <c r="I3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="4" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="4">
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -821,18 +864,22 @@
       <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="K4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <v>3</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -850,18 +897,22 @@
       <c r="I5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="4">
         <v>3</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -879,18 +930,22 @@
       <c r="I6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="7" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" s="4"/>
+    </row>
+    <row r="7" spans="2:12" ht="34" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <v>3</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -908,18 +963,24 @@
       <c r="I7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="8" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K7" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="4">
         <v>3</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -937,18 +998,22 @@
       <c r="I8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="6" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="9" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K8" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" s="4"/>
+    </row>
+    <row r="9" spans="2:12" ht="34" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -966,18 +1031,24 @@
       <c r="I9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="10" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K9" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="34" x14ac:dyDescent="0.2">
       <c r="B10" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="4">
         <v>3</v>
       </c>
       <c r="E10" s="4" t="s">
@@ -995,18 +1066,24 @@
       <c r="I10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="6" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="11" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K10" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="3">
         <v>3</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -1024,18 +1101,22 @@
       <c r="I11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="12" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K11" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B12" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="4">
         <v>36</v>
       </c>
       <c r="E12" s="4" t="s">
@@ -1053,18 +1134,20 @@
       <c r="I12" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="13" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K12" s="6"/>
+      <c r="L12" s="4"/>
+    </row>
+    <row r="13" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="3">
         <v>24</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -1082,18 +1165,20 @@
       <c r="I13" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="14" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K13" s="5"/>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B14" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="4">
         <v>24</v>
       </c>
       <c r="E14" s="4" t="s">
@@ -1111,18 +1196,20 @@
       <c r="I14" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="6" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="15" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K14" s="6"/>
+      <c r="L14" s="4"/>
+    </row>
+    <row r="15" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="3">
         <v>24</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -1140,18 +1227,20 @@
       <c r="I15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="16" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K15" s="5"/>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="4">
         <v>36</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -1169,18 +1258,20 @@
       <c r="I16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="17" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K16" s="6"/>
+      <c r="L16" s="4"/>
+    </row>
+    <row r="17" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="3">
         <v>6</v>
       </c>
       <c r="E17" s="3" t="s">
@@ -1198,18 +1289,20 @@
       <c r="I17" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="K17" s="5"/>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B18" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="4">
         <v>42</v>
       </c>
       <c r="E18" s="4" t="s">
@@ -1227,18 +1320,20 @@
       <c r="I18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="6" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="K18" s="6"/>
+      <c r="L18" s="4"/>
+    </row>
+    <row r="19" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="3">
         <v>1</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -1256,18 +1351,20 @@
       <c r="I19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="20" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K19" s="5"/>
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B20" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="4">
         <v>6</v>
       </c>
       <c r="E20" s="4" t="s">
@@ -1285,18 +1382,20 @@
       <c r="I20" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J20" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K20" s="6"/>
+      <c r="L20" s="4"/>
+    </row>
+    <row r="21" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="3">
         <v>3</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -1314,18 +1413,20 @@
       <c r="I21" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J21" s="6" t="s">
+      <c r="J21" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="22" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K21" s="5"/>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B22" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="4">
         <v>3</v>
       </c>
       <c r="E22" s="4" t="s">
@@ -1343,18 +1444,20 @@
       <c r="I22" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J22" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="23" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="K22" s="6"/>
+      <c r="L22" s="4"/>
+    </row>
+    <row r="23" spans="2:12" ht="17" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="3">
         <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -1372,9 +1475,11 @@
       <c r="I23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="5" t="s">
         <v>82</v>
       </c>
+      <c r="K23" s="5"/>
+      <c r="L23" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Plan/PERT Sheet .xlsx
+++ b/Plan/PERT Sheet .xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stuartbaker/Desktop/University/Year2/Software Engineering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93F180D2-BFA7-8C40-9E82-DC8D50C842ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA21CB12-267E-7D41-BE27-3B351094291D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15980" xr2:uid="{409E12EB-2986-7040-875A-ECA154068229}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15980" activeTab="1" xr2:uid="{409E12EB-2986-7040-875A-ECA154068229}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="PERT Main" sheetId="1" r:id="rId1"/>
+    <sheet name="Pert Additional" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="126">
   <si>
     <t>Task</t>
   </si>
@@ -321,6 +322,99 @@
   </si>
   <si>
     <t>Later start for this as we were focussed on other aspects of the game. This was not a priority at the time and also wasn't part of the critical path so we had some slack time.</t>
+  </si>
+  <si>
+    <t>Overruling Task</t>
+  </si>
+  <si>
+    <t>J, K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementing the rules </t>
+  </si>
+  <si>
+    <t>Implementing the basic actions, such as moving around the board and dice rolling</t>
+  </si>
+  <si>
+    <t>Paying rent</t>
+  </si>
+  <si>
+    <t>Mortgaging a property</t>
+  </si>
+  <si>
+    <t>Ability to purchase a property and its houses / hotel</t>
+  </si>
+  <si>
+    <t>Game modes</t>
+  </si>
+  <si>
+    <t>Coding time limit</t>
+  </si>
+  <si>
+    <t>J, L</t>
+  </si>
+  <si>
+    <t>Implementing board design</t>
+  </si>
+  <si>
+    <t>Players position on board being visible</t>
+  </si>
+  <si>
+    <t>Players money being visible</t>
+  </si>
+  <si>
+    <t>Implementation of visible actions</t>
+  </si>
+  <si>
+    <t>UI for starting the game</t>
+  </si>
+  <si>
+    <t>Zoom in and out feature</t>
+  </si>
+  <si>
+    <t>J, M</t>
+  </si>
+  <si>
+    <t>Difficulty levels</t>
+  </si>
+  <si>
+    <t>Behaviour</t>
+  </si>
+  <si>
+    <t>Auction</t>
+  </si>
+  <si>
+    <t>Task ID</t>
+  </si>
+  <si>
+    <t>N/a</t>
+  </si>
+  <si>
+    <t>Uploading game data</t>
+  </si>
+  <si>
+    <t>3, 15</t>
+  </si>
+  <si>
+    <t>2, 15</t>
+  </si>
+  <si>
+    <t>Day 24</t>
+  </si>
+  <si>
+    <t>Day 30</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 5, 8</t>
+  </si>
+  <si>
+    <t>Day 21</t>
+  </si>
+  <si>
+    <t>Day 27</t>
+  </si>
+  <si>
+    <t>Day 33</t>
   </si>
 </sst>
 </file>
@@ -401,7 +495,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -415,11 +509,26 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -831,10 +940,10 @@
       <c r="I3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>85</v>
       </c>
       <c r="L3" s="3"/>
@@ -864,10 +973,10 @@
       <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>86</v>
       </c>
       <c r="L4" s="4"/>
@@ -897,10 +1006,10 @@
       <c r="I5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="6" t="s">
         <v>86</v>
       </c>
       <c r="L5" s="3"/>
@@ -930,10 +1039,10 @@
       <c r="I6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="7" t="s">
         <v>87</v>
       </c>
       <c r="L6" s="4"/>
@@ -963,10 +1072,10 @@
       <c r="I7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="6" t="s">
         <v>88</v>
       </c>
       <c r="L7" s="3" t="s">
@@ -998,10 +1107,10 @@
       <c r="I8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="7" t="s">
         <v>88</v>
       </c>
       <c r="L8" s="4"/>
@@ -1031,10 +1140,10 @@
       <c r="I9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="6" t="s">
         <v>91</v>
       </c>
       <c r="L9" s="3" t="s">
@@ -1066,10 +1175,10 @@
       <c r="I10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="7" t="s">
         <v>93</v>
       </c>
       <c r="L10" s="4" t="s">
@@ -1101,10 +1210,10 @@
       <c r="I11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="6" t="s">
         <v>88</v>
       </c>
       <c r="L11" s="3"/>
@@ -1134,10 +1243,10 @@
       <c r="I12" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="6"/>
+      <c r="K12" s="7"/>
       <c r="L12" s="4"/>
     </row>
     <row r="13" spans="2:12" ht="17" x14ac:dyDescent="0.2">
@@ -1165,10 +1274,10 @@
       <c r="I13" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="K13" s="5"/>
+      <c r="K13" s="6"/>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" ht="17" x14ac:dyDescent="0.2">
@@ -1196,10 +1305,10 @@
       <c r="I14" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="K14" s="6"/>
+      <c r="K14" s="7"/>
       <c r="L14" s="4"/>
     </row>
     <row r="15" spans="2:12" ht="17" x14ac:dyDescent="0.2">
@@ -1227,10 +1336,10 @@
       <c r="I15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="K15" s="5"/>
+      <c r="K15" s="6"/>
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="2:12" ht="17" x14ac:dyDescent="0.2">
@@ -1258,10 +1367,10 @@
       <c r="I16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="K16" s="6"/>
+      <c r="K16" s="7"/>
       <c r="L16" s="4"/>
     </row>
     <row r="17" spans="2:12" ht="17" x14ac:dyDescent="0.2">
@@ -1289,10 +1398,10 @@
       <c r="I17" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="K17" s="5"/>
+      <c r="K17" s="6"/>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="2:12" ht="17" x14ac:dyDescent="0.2">
@@ -1320,10 +1429,10 @@
       <c r="I18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="K18" s="6"/>
+      <c r="K18" s="7"/>
       <c r="L18" s="4"/>
     </row>
     <row r="19" spans="2:12" ht="17" x14ac:dyDescent="0.2">
@@ -1351,10 +1460,10 @@
       <c r="I19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="K19" s="5"/>
+      <c r="K19" s="6"/>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="2:12" ht="17" x14ac:dyDescent="0.2">
@@ -1382,10 +1491,10 @@
       <c r="I20" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="J20" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="K20" s="6"/>
+      <c r="K20" s="7"/>
       <c r="L20" s="4"/>
     </row>
     <row r="21" spans="2:12" ht="17" x14ac:dyDescent="0.2">
@@ -1413,10 +1522,10 @@
       <c r="I21" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="K21" s="5"/>
+      <c r="K21" s="6"/>
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="2:12" ht="17" x14ac:dyDescent="0.2">
@@ -1444,10 +1553,10 @@
       <c r="I22" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J22" s="6" t="s">
+      <c r="J22" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="K22" s="6"/>
+      <c r="K22" s="7"/>
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="2:12" ht="17" x14ac:dyDescent="0.2">
@@ -1475,13 +1584,708 @@
       <c r="I23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J23" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="K23" s="5"/>
+      <c r="K23" s="6"/>
       <c r="L23" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C313693-B75C-BE42-B20C-B48DF14700FC}">
+  <dimension ref="B2:M23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="B2" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="3">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" spans="2:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="4">
+        <v>3</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L4" s="7"/>
+      <c r="M4" s="4"/>
+    </row>
+    <row r="5" spans="2:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="B5" s="3">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B6" s="4">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="4">
+        <v>3</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B7" s="3">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" s="3">
+        <v>3</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L7" s="6"/>
+      <c r="M7" s="3"/>
+    </row>
+    <row r="8" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B8" s="4">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="4">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L8" s="7"/>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B9" s="3">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="3">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J9" s="3">
+        <v>6</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L9" s="6"/>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B10" s="4">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" s="4">
+        <v>6</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" s="7"/>
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B11" s="3">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="3">
+        <v>6</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11" s="3">
+        <v>2</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="6"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B12" s="4">
+        <v>10</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" s="4">
+        <v>6</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L12" s="7"/>
+      <c r="M12" s="4"/>
+    </row>
+    <row r="13" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B13" s="3">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="3">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" s="3">
+        <v>2</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="6"/>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B14" s="4">
+        <v>12</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="4">
+        <v>6</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L14" s="7"/>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B15" s="3">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="3">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" s="3">
+        <v>14</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L15" s="6"/>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B16" s="4">
+        <v>14</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" s="4">
+        <v>12</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L16" s="7"/>
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B17" s="3">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L17" s="6"/>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B18" s="4">
+        <v>16</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="4">
+        <v>6</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J18" s="4">
+        <v>16</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L18" s="7"/>
+      <c r="M18" s="4"/>
+    </row>
+    <row r="19" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="B19" s="3">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="3">
+        <v>6</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L19" s="6"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="8"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="8"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="8"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="J5:J6 J10" twoDigitTextYear="1"/>
+  </ignoredErrors>
+</worksheet>
 </file>